--- a/docs/lightml/COVERAGE_REPORT.xlsx
+++ b/docs/lightml/COVERAGE_REPORT.xlsx
@@ -463,7 +463,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C10"/>
+  <dimension ref="A1:C11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -511,15 +511,15 @@
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>Profiles with Source JSON (Active)</t>
+          <t>Technically Mature Profiles (Active)</t>
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>19.6%</t>
         </is>
       </c>
     </row>
@@ -571,15 +571,30 @@
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>Profiles with Validation Evidence</t>
+          <t>Profiles with Legal Evidence Packages Completed</t>
         </is>
       </c>
       <c r="B10" s="5" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>19.6%</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Profiles with Legal Review/Approval Completed</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>0</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
@@ -662,7 +677,7 @@
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Technically Mature</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
@@ -704,7 +719,7 @@
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Technically Mature</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
@@ -746,7 +761,7 @@
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Technically Mature</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
@@ -788,7 +803,7 @@
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Technically Mature</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
@@ -830,7 +845,7 @@
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Technically Mature</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
@@ -872,7 +887,7 @@
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Technically Mature</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
@@ -914,7 +929,7 @@
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Technically Mature</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
@@ -956,7 +971,7 @@
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Technically Mature</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
@@ -998,7 +1013,7 @@
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Technically Mature</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
@@ -1040,7 +1055,7 @@
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Technically Mature</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
@@ -1082,7 +1097,7 @@
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>Draft / Incomplete</t>
+          <t>Partially Usable</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
@@ -1124,7 +1139,7 @@
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>Draft / Incomplete</t>
+          <t>Partially Usable</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
@@ -1166,7 +1181,7 @@
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>Draft / Incomplete</t>
+          <t>Partially Usable</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
@@ -1208,7 +1223,7 @@
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>Draft / Incomplete</t>
+          <t>Partially Usable</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
@@ -1250,7 +1265,7 @@
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>Draft / Incomplete</t>
+          <t>Partially Usable</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
@@ -1292,7 +1307,7 @@
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>Draft / Incomplete</t>
+          <t>Partially Usable</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
@@ -1334,7 +1349,7 @@
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Partially Usable</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
@@ -1359,7 +1374,7 @@
       </c>
       <c r="H18" s="5" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1376,7 +1391,7 @@
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>Draft / Incomplete</t>
+          <t>Partially Usable</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
@@ -1418,7 +1433,7 @@
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Partially Usable</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
@@ -1443,7 +1458,7 @@
       </c>
       <c r="H20" s="5" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1460,7 +1475,7 @@
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>Draft / Incomplete</t>
+          <t>Partially Usable</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
@@ -1502,7 +1517,7 @@
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>Draft / Incomplete</t>
+          <t>Partially Usable</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
@@ -1544,7 +1559,7 @@
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>Draft / Incomplete</t>
+          <t>Partially Usable</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
@@ -1586,7 +1601,7 @@
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>Draft / Incomplete</t>
+          <t>Partially Usable</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
@@ -1628,7 +1643,7 @@
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>Draft / Incomplete</t>
+          <t>Partially Usable</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
@@ -1670,7 +1685,7 @@
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>Draft / Incomplete</t>
+          <t>Partially Usable</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
@@ -1712,7 +1727,7 @@
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>Draft / Incomplete</t>
+          <t>Partially Usable</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
@@ -1754,7 +1769,7 @@
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>Draft / Incomplete</t>
+          <t>Partially Usable</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
@@ -1796,7 +1811,7 @@
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>Draft / Incomplete</t>
+          <t>Partially Usable</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
@@ -1838,7 +1853,7 @@
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>Draft / Incomplete</t>
+          <t>Partially Usable</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
@@ -1880,7 +1895,7 @@
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>Draft / Incomplete</t>
+          <t>Partially Usable</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
@@ -1922,7 +1937,7 @@
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Partially Usable</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
@@ -1947,7 +1962,7 @@
       </c>
       <c r="H32" s="5" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1964,7 +1979,7 @@
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>Draft / Incomplete</t>
+          <t>Partially Usable</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
@@ -2006,7 +2021,7 @@
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>Draft / Incomplete</t>
+          <t>Partially Usable</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
@@ -2048,7 +2063,7 @@
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>Draft / Incomplete</t>
+          <t>Partially Usable</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
@@ -2090,7 +2105,7 @@
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>Draft / Incomplete</t>
+          <t>Partially Usable</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
@@ -2132,7 +2147,7 @@
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>Draft / Incomplete</t>
+          <t>Partially Usable</t>
         </is>
       </c>
       <c r="D37" s="5" t="inlineStr">
@@ -2174,7 +2189,7 @@
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>Draft / Incomplete</t>
+          <t>Partially Usable</t>
         </is>
       </c>
       <c r="D38" s="5" t="inlineStr">
@@ -2216,7 +2231,7 @@
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>Draft / Incomplete</t>
+          <t>Partially Usable</t>
         </is>
       </c>
       <c r="D39" s="5" t="inlineStr">
@@ -2258,7 +2273,7 @@
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>Draft / Incomplete</t>
+          <t>Partially Usable</t>
         </is>
       </c>
       <c r="D40" s="5" t="inlineStr">
@@ -2300,7 +2315,7 @@
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>Draft / Incomplete</t>
+          <t>Partially Usable</t>
         </is>
       </c>
       <c r="D41" s="5" t="inlineStr">
@@ -2342,7 +2357,7 @@
       </c>
       <c r="C42" s="5" t="inlineStr">
         <is>
-          <t>Draft / Incomplete</t>
+          <t>Partially Usable</t>
         </is>
       </c>
       <c r="D42" s="5" t="inlineStr">
@@ -2384,7 +2399,7 @@
       </c>
       <c r="C43" s="5" t="inlineStr">
         <is>
-          <t>Draft / Incomplete</t>
+          <t>Partially Usable</t>
         </is>
       </c>
       <c r="D43" s="5" t="inlineStr">
@@ -2426,7 +2441,7 @@
       </c>
       <c r="C44" s="5" t="inlineStr">
         <is>
-          <t>Draft / Incomplete</t>
+          <t>Partially Usable</t>
         </is>
       </c>
       <c r="D44" s="5" t="inlineStr">
@@ -2468,7 +2483,7 @@
       </c>
       <c r="C45" s="5" t="inlineStr">
         <is>
-          <t>Draft / Incomplete</t>
+          <t>Partially Usable</t>
         </is>
       </c>
       <c r="D45" s="5" t="inlineStr">
@@ -2510,7 +2525,7 @@
       </c>
       <c r="C46" s="5" t="inlineStr">
         <is>
-          <t>Draft / Incomplete</t>
+          <t>Partially Usable</t>
         </is>
       </c>
       <c r="D46" s="5" t="inlineStr">
@@ -2552,7 +2567,7 @@
       </c>
       <c r="C47" s="5" t="inlineStr">
         <is>
-          <t>Draft / Incomplete</t>
+          <t>Partially Usable</t>
         </is>
       </c>
       <c r="D47" s="5" t="inlineStr">
@@ -2594,7 +2609,7 @@
       </c>
       <c r="C48" s="5" t="inlineStr">
         <is>
-          <t>Draft / Incomplete</t>
+          <t>Partially Usable</t>
         </is>
       </c>
       <c r="D48" s="5" t="inlineStr">
@@ -2636,7 +2651,7 @@
       </c>
       <c r="C49" s="5" t="inlineStr">
         <is>
-          <t>Draft / Incomplete</t>
+          <t>Partially Usable</t>
         </is>
       </c>
       <c r="D49" s="5" t="inlineStr">
@@ -2678,7 +2693,7 @@
       </c>
       <c r="C50" s="5" t="inlineStr">
         <is>
-          <t>Draft / Incomplete</t>
+          <t>Partially Usable</t>
         </is>
       </c>
       <c r="D50" s="5" t="inlineStr">
@@ -2720,7 +2735,7 @@
       </c>
       <c r="C51" s="5" t="inlineStr">
         <is>
-          <t>Draft / Incomplete</t>
+          <t>Partially Usable</t>
         </is>
       </c>
       <c r="D51" s="5" t="inlineStr">
@@ -2762,7 +2777,7 @@
       </c>
       <c r="C52" s="5" t="inlineStr">
         <is>
-          <t>Draft / Incomplete</t>
+          <t>Partially Usable</t>
         </is>
       </c>
       <c r="D52" s="5" t="inlineStr">
@@ -2804,7 +2819,7 @@
       </c>
       <c r="C53" s="5" t="inlineStr">
         <is>
-          <t>Draft / Incomplete</t>
+          <t>Partially Usable</t>
         </is>
       </c>
       <c r="D53" s="5" t="inlineStr">
@@ -2846,7 +2861,7 @@
       </c>
       <c r="C54" s="5" t="inlineStr">
         <is>
-          <t>Draft / Incomplete</t>
+          <t>Partially Usable</t>
         </is>
       </c>
       <c r="D54" s="5" t="inlineStr">
@@ -2888,7 +2903,7 @@
       </c>
       <c r="C55" s="5" t="inlineStr">
         <is>
-          <t>Draft / Incomplete</t>
+          <t>Partially Usable</t>
         </is>
       </c>
       <c r="D55" s="5" t="inlineStr">
@@ -2930,7 +2945,7 @@
       </c>
       <c r="C56" s="5" t="inlineStr">
         <is>
-          <t>Draft / Incomplete</t>
+          <t>Partially Usable</t>
         </is>
       </c>
       <c r="D56" s="5" t="inlineStr">
@@ -2972,7 +2987,7 @@
       </c>
       <c r="C57" s="5" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Technically Mature</t>
         </is>
       </c>
       <c r="D57" s="5" t="inlineStr">

--- a/docs/lightml/COVERAGE_REPORT.xlsx
+++ b/docs/lightml/COVERAGE_REPORT.xlsx
@@ -530,12 +530,10 @@
         </is>
       </c>
       <c r="B7" s="5" t="n">
-        <v>42</v>
-      </c>
-      <c r="C7" s="5" t="inlineStr">
-        <is>
-          <t>75.0%</t>
-        </is>
+        <v>45</v>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>0.804</v>
       </c>
     </row>
     <row r="8">
@@ -571,7 +569,7 @@
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>Profiles with Legal Evidence Packages Completed</t>
+          <t>Profiles with Repository-supported Legal Evidence Package Prepared</t>
         </is>
       </c>
       <c r="B10" s="5" t="n">
@@ -1359,7 +1357,7 @@
       </c>
       <c r="E18" s="5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F18" s="5" t="inlineStr">
@@ -1443,7 +1441,7 @@
       </c>
       <c r="E20" s="5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F20" s="5" t="inlineStr">
@@ -1947,7 +1945,7 @@
       </c>
       <c r="E32" s="5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F32" s="5" t="inlineStr">
